--- a/kname_webapp/result_brazil.xlsx
+++ b/kname_webapp/result_brazil.xlsx
@@ -4746,12 +4746,12 @@
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>Someone refined as a treasure</t>
+          <t>A clear, precious treasure of spirit</t>
         </is>
       </c>
       <c r="L60" s="4" t="inlineStr">
         <is>
-          <t>Boa carries a quiet richness: 보 (寶) for treasure, 아 (雅) for clarity and grace, together whispering a hope that someone might hold something precious within them, plainly and beautifully, without needing ornament to prove its worth. Spoken aloud, the name is soft and rounded, its open vowels unfolding like a small sigh of ease. That same gentle brightness carries into Poliana, their English name, echoing outward as a treasure clearly, gracefully seen.</t>
+          <t>보아 (寶雅, Boa) joins 寶, treasure, with 雅, clear, weaving together the hope that someone would carry a clarity so pure it becomes precious — a mind and spirit valued not for glitter but for honest, luminous grace. Spoken aloud, the name is light and open, two clean syllables rounding softly from lips to breath, gentle yet confident. Abroad, it echoes comfortably into Poliana, easy for new tongues to hold, while at its heart it still means something rarer: a clear treasure, simply and quietly whole.</t>
         </is>
       </c>
       <c r="M60" s="4" t="inlineStr">
@@ -5456,12 +5456,12 @@
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>Someone bright as silk</t>
+          <t>Brightness spreading warmly to others</t>
         </is>
       </c>
       <c r="L70" s="4" t="inlineStr">
         <is>
-          <t>Sora carries a quiet radiance: 소, bright, joined with 라, to spread, so the name itself means something like brightness unfurling outward — light that doesn't stay still. Spoken aloud, it's soft yet clear, opening on that wide "o" before settling into the crisp lift of "ra." Names like Soyul, Soyun, Rahui, and Ara echo its bright, gentle music. Fittingly, Solange, their English name, holds its own quiet glow, an echo across languages.</t>
+          <t>소라 (昭羅, Sora) joins 昭, meaning bright, with 羅, meaning to spread, painting the wish that one's brightness might spread outward, touching everyone nearby like sunlight unfurling across a room. It sits alongside names like 소율, 소윤, 라희, and 아라, each carrying its own quiet radiance. Spoken aloud, 소라 flows softly, its open vowels rounding gently, crisp yet warm on the tongue. Abroad, it echoes comfortably in Solange, easing its way into new mouths without losing its light.</t>
         </is>
       </c>
       <c r="M70" s="4" t="inlineStr">
@@ -5598,12 +5598,12 @@
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>Someone great as a river</t>
+          <t>Vast, generous strength like a great river</t>
         </is>
       </c>
       <c r="L72" s="4" t="inlineStr">
         <is>
-          <t>Taeha carries the image of a great river—broad, unhurried, and quietly powerful, the kind of water that carves canyons simply by persisting. It's a name that hopes for someone with that same steady strength, generous and expansive rather than loud. Spoken aloud, Taeha flows easily: a crisp opening breath, then open, sunny vowels that glide together like current over smooth stone. That same easy openness carries into Thiago, its English echo—warm, rounded, effortless to say across languages.</t>
+          <t>태하 (泰河, Taeha) joins a river's steady flow with the idea of greatness, painting the image of a great river — wide, generous, unhurried, carrying strength quietly onward wherever it goes. It's a wish for someone whose presence broadens and deepens with time, rather than rushing or straining. Spoken aloud, Taeha feels open and clear: the bright "tae" gives way to the soft, breathy "ha," two syllables that glide easily off the tongue. Abroad, its rhythm echoes gently in the name Thiago, making it easy to say and recognize.</t>
         </is>
       </c>
       <c r="M72" s="4" t="inlineStr">
@@ -6379,12 +6379,12 @@
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>Someone luxuriant as the Han River</t>
+          <t>A river's grace paired with a daughter's tender</t>
         </is>
       </c>
       <c r="L83" s="4" t="inlineStr">
         <is>
-          <t>Han-ul carries the breadth of the Han River flowing through its first syllable, paired with a character meaning son—an unusual pairing that quietly wishes for tenderness and continuity within a life. Spoken aloud, it opens softly: a clean "hahn" sliding into "ool," gentle and unhurried, like water finding its course. There's a pleasing echo between this name and Fabio—both carry that same soft, open warmth, a sound that feels welcoming rather than sharp, fitting someone whose presence flows easily into a room.</t>
+          <t>한울 (漢蔚, Hanul) joins 한, the wide flow of the Han River, with 울, meaning son, weaving together the river's steady, open grace and the tender warmth held for a beloved son — a wish that this boy carry both strength and gentleness, flowing forward while being cherished close. Spoken aloud, 한울 feels soft and clear, its open vowels rounding gently like water, its consonants clean and unhurried. To ears abroad, it settles comfortably near "Fabio," familiar enough to greet the world with ease.</t>
         </is>
       </c>
       <c r="M83" s="4" t="inlineStr">
@@ -6592,12 +6592,12 @@
       </c>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>Someone beneficial who establishes</t>
+          <t>One who builds lasting benefit for others</t>
         </is>
       </c>
       <c r="L86" s="4" t="inlineStr">
         <is>
-          <t>Igeon carries a quiet strength: 利 for benefit and goodness, 建 for building something lasting — together, a wish that someone's life will construct good into the world, not just pass through it. Spoken aloud, Igeon is crisp yet warm, opening on a soft vowel before settling into that firm, grounded "gun" sound — like a foundation being laid. Fittingly, it echoes the sturdiness of their English name, Igor, another name rooted in strength and steadiness.</t>
+          <t>이건 (利建, Igeon) joins the idea of benefit with the act of building, painting the hope of someone who lays foundations that bring good to others — a life constructed with purpose, where what is built stands solid and useful for years to come. Spoken aloud, the name is quick and clean, its two syllables landing softly with open vowels, easy on the tongue and pleasant to hear. Abroad, it settles comfortably near "Igor," giving it a familiar ring without borrowing any of that name's own meaning.</t>
         </is>
       </c>
       <c r="M86" s="4" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>Someone shining who helps</t>
+          <t>One who helps others while shining bright</t>
         </is>
       </c>
       <c r="L91" s="4" t="inlineStr">
         <is>
-          <t>Woobin carries a quiet strength: 佑 (u) means to help or protect, while 彬 (bin) evokes a refined, shining presence—together suggesting someone destined to support others while radiating quiet brilliance. Spoken aloud, it opens softly on "oo" and closes crisp and bright on "bin," a name that feels gentle yet clear. Fittingly, it echoes into Otavio, another name with warmth and light—one flowing into the other like two languages sharing the same hopeful spirit.</t>
+          <t>우빈 (佑彬, Ubin) joins 佑, help, with 彬, shining, painting the hope of someone who lends quiet aid to others while carrying a natural brightness within — a person meant to assist and to shine at once, radiance offered outward rather than kept for oneself. Spoken aloud, the name flows smoothly: a soft "oo" opening into a crisp, bright "bin," easy and warm on the tongue. Abroad, it settles comfortably beside Otavio, sharing that same gentle, rounded ease of sound.</t>
         </is>
       </c>
       <c r="M91" s="4" t="inlineStr">
@@ -7018,12 +7018,12 @@
       </c>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>Someone luxuriant as the Han River</t>
+          <t>River's steady flow and cherished belonging</t>
         </is>
       </c>
       <c r="L92" s="4" t="inlineStr">
         <is>
-          <t>Hanul carries the wide, flowing spirit of the Han River in its first syllable, paired with 울, a character meaning son—together suggesting someone cherished as deeply as a river cherishes the land it shapes, a quiet hope that they'd be loved without condition. Spoken aloud,</t>
+          <t>한울 (漢蔚, Hanul) joins the flow of the Han River with the quiet devotion carried in the word for son, weaving together an image of steady, life-giving current and tender belonging — as if someone were meant to move through the world with the river's calm strength while holding close the warmth of family ties. Spoken aloud, the name feels open and clear, its vowels wide and unhurried, its consonants soft-edged, giving it a gentle, flowing rhythm. Abroad, it settles comfortably beside the name Paulo, echoing in cadence and easy familiarity.</t>
         </is>
       </c>
       <c r="M92" s="4" t="inlineStr">

--- a/kname_webapp/result_brazil.xlsx
+++ b/kname_webapp/result_brazil.xlsx
@@ -4746,7 +4746,7 @@
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>A clear, precious treasure of spirit</t>
+          <t>Someone refined as a treasure</t>
         </is>
       </c>
       <c r="L60" s="4" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>Brightness spreading warmly to others</t>
+          <t>Someone bright as silk</t>
         </is>
       </c>
       <c r="L70" s="4" t="inlineStr">
@@ -5598,12 +5598,12 @@
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>Vast, generous strength like a great river</t>
+          <t>A vast, generous spirit like a great river</t>
         </is>
       </c>
       <c r="L72" s="4" t="inlineStr">
         <is>
-          <t>태하 (泰河, Taeha) joins a river's steady flow with the idea of greatness, painting the image of a great river — wide, generous, unhurried, carrying strength quietly onward wherever it goes. It's a wish for someone whose presence broadens and deepens with time, rather than rushing or straining. Spoken aloud, Taeha feels open and clear: the bright "tae" gives way to the soft, breathy "ha," two syllables that glide easily off the tongue. Abroad, its rhythm echoes gently in the name Thiago, making it easy to say and recognize.</t>
+          <t>태하 (泰河, Taeha) joins greatness with the river, painting the image of a spirit as vast and enduring as flowing water — someone meant to carry a wide, generous heart and a steady, unstoppable strength through life. Spoken aloud, the name feels smooth and open, its two syllables gliding gently from a bright "tae" into a soft, breathy "ha," warm and easy on the tongue. Abroad, its rhythm echoes pleasantly in the name Thiago, giving it a familiar, welcoming ring.</t>
         </is>
       </c>
       <c r="M72" s="4" t="inlineStr">
@@ -6379,7 +6379,7 @@
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>A river's grace paired with a daughter's tender</t>
+          <t>Someone luxuriant as the Han River</t>
         </is>
       </c>
       <c r="L83" s="4" t="inlineStr">
@@ -6597,7 +6597,7 @@
       </c>
       <c r="L86" s="4" t="inlineStr">
         <is>
-          <t>이건 (利建, Igeon) joins the idea of benefit with the act of building, painting the hope of someone who lays foundations that bring good to others — a life constructed with purpose, where what is built stands solid and useful for years to come. Spoken aloud, the name is quick and clean, its two syllables landing softly with open vowels, easy on the tongue and pleasant to hear. Abroad, it settles comfortably near "Igor," giving it a familiar ring without borrowing any of that name's own meaning.</t>
+          <t>이건 (利建, Igeon) joins 利, meaning beneficial, with 建, to establish, painting the hope that someone will build things of lasting value and bring good wherever their efforts take root — a life spent constructing benefit for others, not just for oneself. Spoken aloud, the name is brisk and clean: a short "i" opening into the firm, grounded "geon," crisp yet warm, easy for English speakers to say. Abroad, it settles comfortably near "Igor," giving someone a familiar echo while keeping its own true, hopeful shape.</t>
         </is>
       </c>
       <c r="M86" s="4" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>One who helps others while shining bright</t>
+          <t>Someone whose brightness becomes a support to others</t>
         </is>
       </c>
       <c r="L91" s="4" t="inlineStr">
         <is>
-          <t>우빈 (佑彬, Ubin) joins 佑, help, with 彬, shining, painting the hope of someone who lends quiet aid to others while carrying a natural brightness within — a person meant to assist and to shine at once, radiance offered outward rather than kept for oneself. Spoken aloud, the name flows smoothly: a soft "oo" opening into a crisp, bright "bin," easy and warm on the tongue. Abroad, it settles comfortably beside Otavio, sharing that same gentle, rounded ease of sound.</t>
+          <t>우빈 (佑彬, Ubin) joins 佑, meaning to help, with 彬, meaning shining, painting the image of someone whose brightness becomes a support to others — a light that steadies rather than dazzles. Parents choosing it often dream of a boy who lifts people up simply by being near them. Spoken aloud, the name flows gently: the rounded "oo" opens into the crisp, clean "bin," soft yet confident. Abroad, it sits comfortably alongside Otavio, both carrying an easy, open rhythm that rolls naturally off the tongue.</t>
         </is>
       </c>
       <c r="M91" s="4" t="inlineStr">
@@ -7018,12 +7018,12 @@
       </c>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>River's steady flow and cherished belonging</t>
+          <t>A life flourishing wide like a river</t>
         </is>
       </c>
       <c r="L92" s="4" t="inlineStr">
         <is>
-          <t>한울 (漢蔚, Hanul) joins the flow of the Han River with the quiet devotion carried in the word for son, weaving together an image of steady, life-giving current and tender belonging — as if someone were meant to move through the world with the river's calm strength while holding close the warmth of family ties. Spoken aloud, the name feels open and clear, its vowels wide and unhurried, its consonants soft-edged, giving it a gentle, flowing rhythm. Abroad, it settles comfortably beside the name Paulo, echoing in cadence and easy familiarity.</t>
+          <t>한울 (漢蔚, Hanul) joins the wide, steady flow of the Han River with the lushness of things flourishing along its banks, holding a hope that this person's life will spread out broad and abundant, never running dry. Alongside cousins like 한결, 지한, 하울, and 시울, it shares that same river-warmth. Spoken aloud, Hanul is soft and open, its vowels rolling easily, faintly echoing the familiar shape of Paulo to English-speaking ears, gentle and easy to carry anywhere.</t>
         </is>
       </c>
       <c r="M92" s="4" t="inlineStr">

--- a/kname_webapp/result_brazil.xlsx
+++ b/kname_webapp/result_brazil.xlsx
@@ -4764,7 +4764,11 @@
           <t>폴→보 partial / 아→아 strong</t>
         </is>
       </c>
-      <c r="O60" s="2" t="inlineStr"/>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>예전캐시(재생성실패)</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
@@ -5456,12 +5460,12 @@
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>Someone bright as silk</t>
+          <t>Bright light unfolding gently like silk</t>
         </is>
       </c>
       <c r="L70" s="4" t="inlineStr">
         <is>
-          <t>소라 (昭羅, Sora) joins 昭, meaning bright, with 羅, meaning to spread, painting the wish that one's brightness might spread outward, touching everyone nearby like sunlight unfurling across a room. It sits alongside names like 소율, 소윤, 라희, and 아라, each carrying its own quiet radiance. Spoken aloud, 소라 flows softly, its open vowels rounding gently, crisp yet warm on the tongue. Abroad, it echoes comfortably in Solange, easing its way into new mouths without losing its light.</t>
+          <t>소라 (昭羅, Sora) joins brightness with silk unfurling — light spreading outward like fine fabric catching a breeze. Together the characters suggest a radiance meant to open gently rather than blaze, a hope that someone might carry clarity that unfolds softly into the world around them. Spoken aloud, the name is light and rounded, its open vowels giving it a gentle, airy lilt, easy and pleasant on the tongue. Abroad, it settles comfortably near Solange, the echo of sound making it feel instantly familiar without losing its own quiet shine.</t>
         </is>
       </c>
       <c r="M70" s="4" t="inlineStr">
@@ -6397,7 +6401,11 @@
           <t>파→한 loose / 우→울 strong</t>
         </is>
       </c>
-      <c r="O83" s="2" t="inlineStr"/>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>예전캐시(재생성실패)</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
@@ -7689,7 +7697,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -7753,10 +7761,10 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C6" s="8" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="8">
@@ -7886,19 +7894,32 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="7" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>예전캐시(재생성실패)</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="C20" s="8" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>서로 다른 결과 이름</t>
         </is>
       </c>
-      <c r="B21" s="7" t="n">
+      <c r="B22" s="7" t="n">
         <v>96</v>
       </c>
-      <c r="C21" s="8" t="n">
+      <c r="C22" s="8" t="n">
         <v>0.96</v>
       </c>
-      <c r="D21" s="9" t="inlineStr">
+      <c r="D22" s="9" t="inlineStr">
         <is>
           <t>다양성 — 높을수록 좋음</t>
         </is>
